--- a/esempi/esempio_turno_dopo.xlsx
+++ b/esempi/esempio_turno_dopo.xlsx
@@ -1483,7 +1483,7 @@
       <c r="B7" s="87" t="n"/>
       <c r="C7" s="88" t="n"/>
       <c r="D7" s="26" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="E7" s="53" t="n"/>
       <c r="F7" s="87" t="n"/>
@@ -2078,7 +2078,9 @@
       <c r="F24" s="87" t="n"/>
       <c r="G24" s="88" t="n"/>
       <c r="H24" s="6" t="n"/>
-      <c r="I24" s="74" t="n"/>
+      <c r="I24" s="74" t="n">
+        <v>0.5871759259259259</v>
+      </c>
       <c r="J24" s="87" t="n"/>
       <c r="K24" s="88" t="n"/>
       <c r="L24" s="1" t="inlineStr">
@@ -2208,7 +2210,9 @@
       <c r="F28" s="87" t="n"/>
       <c r="G28" s="88" t="n"/>
       <c r="H28" s="6" t="n"/>
-      <c r="I28" s="45" t="n"/>
+      <c r="I28" s="45" t="n">
+        <v>20</v>
+      </c>
       <c r="J28" s="87" t="n"/>
       <c r="K28" s="88" t="n"/>
       <c r="L28" s="100" t="n"/>
